--- a/Cplusplus/00. CPlusPlus CheckList.xlsx
+++ b/Cplusplus/00. CPlusPlus CheckList.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="779">
   <si>
     <t>[ ] Branching strategies (gitflow, feature branches)</t>
   </si>
@@ -3695,13 +3695,54 @@
   </si>
   <si>
     <t>C++ FOUNDATIONS</t>
+  </si>
+  <si>
+    <t>4. Modern C++ keywords</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>[] 14. inline variables (C++17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[] 15. extern </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t>[ ]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Thread trong C++ 98</t>
+    </r>
+  </si>
+  <si>
+    <t>[ ] POSIX Threads (pthread)</t>
+  </si>
+  <si>
+    <t>[ ] Windows Threads — Win32 API</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3735,6 +3776,21 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3787,7 +3843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3812,6 +3868,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5274,41 +5337,41 @@
         <v>39</v>
       </c>
     </row>
-    <row r="97" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:37" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:52" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="99" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:37" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="104" spans="1:52" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="105" spans="1:37" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:52" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>45</v>
       </c>
@@ -5318,8 +5381,11 @@
       <c r="AK105" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="106" spans="1:37" ht="15" x14ac:dyDescent="0.2">
+      <c r="AX105" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="106" spans="1:52" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
         <v>400</v>
       </c>
@@ -5329,8 +5395,11 @@
       <c r="AK106" s="3" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="107" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AX106" s="3" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="107" spans="1:52" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>46</v>
       </c>
@@ -5340,8 +5409,13 @@
       <c r="AK107" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="108" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AX107" s="13" t="s">
+        <v>774</v>
+      </c>
+      <c r="AY107" s="12"/>
+      <c r="AZ107" s="12"/>
+    </row>
+    <row r="108" spans="1:52" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>47</v>
       </c>
@@ -5351,8 +5425,13 @@
       <c r="AK108" s="4" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="109" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AX108" s="13" t="s">
+        <v>775</v>
+      </c>
+      <c r="AY108" s="12"/>
+      <c r="AZ108" s="12"/>
+    </row>
+    <row r="109" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>48</v>
       </c>
@@ -5362,8 +5441,9 @@
       <c r="AK109" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="110" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AX109" s="4"/>
+    </row>
+    <row r="110" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>49</v>
       </c>
@@ -5373,13 +5453,15 @@
       <c r="AK110" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="111" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AX110" s="4"/>
+    </row>
+    <row r="111" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A111" s="3"/>
       <c r="S111" s="3"/>
       <c r="AK111" s="3"/>
-    </row>
-    <row r="112" spans="1:37" ht="15" x14ac:dyDescent="0.2">
+      <c r="AX111" s="3"/>
+    </row>
+    <row r="112" spans="1:52" ht="15" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
         <v>401</v>
       </c>
@@ -5389,6 +5471,7 @@
       <c r="AK112" s="3" t="s">
         <v>412</v>
       </c>
+      <c r="AX112" s="3"/>
     </row>
     <row r="113" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
@@ -5400,6 +5483,7 @@
       <c r="AK113" s="4" t="s">
         <v>413</v>
       </c>
+      <c r="AX113" s="4"/>
     </row>
     <row r="114" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
@@ -5411,6 +5495,7 @@
       <c r="AK114" s="4" t="s">
         <v>414</v>
       </c>
+      <c r="AX114" s="4"/>
     </row>
     <row r="115" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
@@ -5422,6 +5507,7 @@
       <c r="AK115" s="4" t="s">
         <v>415</v>
       </c>
+      <c r="AX115" s="4"/>
     </row>
     <row r="116" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
@@ -5690,8 +5776,8 @@
       </c>
     </row>
     <row r="146" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="s">
-        <v>457</v>
+      <c r="A146" s="14" t="s">
+        <v>776</v>
       </c>
       <c r="R146" s="3" t="s">
         <v>462</v>
@@ -5705,7 +5791,7 @@
     </row>
     <row r="147" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
-        <v>458</v>
+        <v>777</v>
       </c>
       <c r="R147" s="4" t="s">
         <v>463</v>
@@ -5719,7 +5805,7 @@
     </row>
     <row r="148" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>79</v>
+        <v>778</v>
       </c>
       <c r="R148" s="4" t="s">
         <v>464</v>
@@ -5732,9 +5818,6 @@
       </c>
     </row>
     <row r="149" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A149" s="4" t="s">
-        <v>459</v>
-      </c>
       <c r="R149" s="4" t="s">
         <v>465</v>
       </c>
@@ -5745,9 +5828,9 @@
         <v>481</v>
       </c>
     </row>
-    <row r="150" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A150" s="4" t="s">
-        <v>80</v>
+    <row r="150" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="R150" s="4" t="s">
         <v>466</v>
@@ -5760,13 +5843,15 @@
       </c>
     </row>
     <row r="151" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A151" s="3"/>
+      <c r="A151" s="4" t="s">
+        <v>458</v>
+      </c>
       <c r="R151" s="3"/>
       <c r="AG151" s="3"/>
     </row>
     <row r="152" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A152" s="3" t="s">
-        <v>460</v>
+      <c r="A152" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="R152" s="3" t="s">
         <v>467</v>
@@ -5777,7 +5862,7 @@
     </row>
     <row r="153" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="R153" s="4" t="s">
         <v>468</v>
@@ -5788,7 +5873,7 @@
     </row>
     <row r="154" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R154" s="4" t="s">
         <v>469</v>
@@ -5798,9 +5883,7 @@
       </c>
     </row>
     <row r="155" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A155" s="4" t="s">
-        <v>82</v>
-      </c>
+      <c r="A155" s="3"/>
       <c r="R155" s="4" t="s">
         <v>470</v>
       </c>
@@ -5808,20 +5891,32 @@
         <v>91</v>
       </c>
     </row>
-    <row r="156" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
+        <v>460</v>
+      </c>
       <c r="R156" s="4" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="157" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A157" s="4" t="s">
+        <v>461</v>
+      </c>
       <c r="R157" s="3"/>
     </row>
     <row r="158" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="A158" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="R158" s="3" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="159" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A159" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="R159" s="4" t="s">
         <v>473</v>
       </c>

--- a/Cplusplus/00. CPlusPlus CheckList.xlsx
+++ b/Cplusplus/00. CPlusPlus CheckList.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="787">
   <si>
     <t>[ ] Branching strategies (gitflow, feature branches)</t>
   </si>
@@ -3736,6 +3736,78 @@
   </si>
   <si>
     <t>[ ] Windows Threads — Win32 API</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[ ] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Synchronous</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[ ] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Asynchronous</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[ ] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Semaphore   </t>
+    </r>
+  </si>
+  <si>
+    <t>[ ] std::counting_semaphore&lt;N&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[ ] std::binary_semaphore   </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[ ] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>PSEUDO CODE VxWorks PATTERN</t>
+    </r>
+  </si>
+  <si>
+    <t>[ ] example</t>
   </si>
 </sst>
 </file>
@@ -4209,79 +4281,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:DP316"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:DP326"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:58" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="2" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="3" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>346</v>
       </c>
       <c r="B3" s="7"/>
     </row>
-    <row r="4" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="7"/>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="13" spans="1:58" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:58" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:58" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:58" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="15" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>4</v>
       </c>
@@ -4295,7 +4367,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:58" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>351</v>
       </c>
@@ -4309,7 +4381,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="17" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>352</v>
       </c>
@@ -4323,7 +4395,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="18" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>353</v>
       </c>
@@ -4337,7 +4409,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="19" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>354</v>
       </c>
@@ -4351,7 +4423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>355</v>
       </c>
@@ -4363,7 +4435,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:105" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="S21" s="3" t="s">
         <v>364</v>
@@ -4371,7 +4443,7 @@
       <c r="AM21" s="3"/>
       <c r="BF21" s="3"/>
     </row>
-    <row r="22" spans="1:105" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>356</v>
       </c>
@@ -4385,7 +4457,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="23" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>357</v>
       </c>
@@ -4399,7 +4471,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="24" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>358</v>
       </c>
@@ -4413,7 +4485,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="25" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>359</v>
       </c>
@@ -4424,7 +4496,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="26" spans="1:105" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:105" x14ac:dyDescent="0.25">
       <c r="AM26" s="4" t="s">
         <v>370</v>
       </c>
@@ -4432,13 +4504,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:105" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:105" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:105" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:105" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="29" spans="1:105" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:105" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>594</v>
       </c>
@@ -4455,7 +4527,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="30" spans="1:105" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:105" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>595</v>
       </c>
@@ -4475,7 +4547,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="31" spans="1:105" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:105" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>716</v>
       </c>
@@ -4495,7 +4567,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="32" spans="1:105" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:105" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>717</v>
       </c>
@@ -4515,7 +4587,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="33" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>718</v>
       </c>
@@ -4535,7 +4607,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="34" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>719</v>
       </c>
@@ -4555,7 +4627,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="35" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>596</v>
       </c>
@@ -4573,7 +4645,7 @@
       </c>
       <c r="DA35" s="2"/>
     </row>
-    <row r="36" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>597</v>
       </c>
@@ -4591,7 +4663,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="37" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="W37" s="1" t="s">
         <v>629</v>
@@ -4605,7 +4677,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="38" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>598</v>
       </c>
@@ -4623,7 +4695,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="39" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>599</v>
       </c>
@@ -4643,7 +4715,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="40" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>600</v>
       </c>
@@ -4663,7 +4735,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="41" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>601</v>
       </c>
@@ -4681,7 +4753,7 @@
       </c>
       <c r="DA41" s="2"/>
     </row>
-    <row r="42" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>602</v>
       </c>
@@ -4699,7 +4771,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="43" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>378</v>
       </c>
@@ -4727,7 +4799,7 @@
       <c r="DJ43" s="2"/>
       <c r="DK43" s="2"/>
     </row>
-    <row r="44" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>720</v>
       </c>
@@ -4762,7 +4834,7 @@
       <c r="DO44" s="2"/>
       <c r="DP44" s="2"/>
     </row>
-    <row r="45" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>721</v>
       </c>
@@ -4795,7 +4867,7 @@
       <c r="DO45" s="2"/>
       <c r="DP45" s="2"/>
     </row>
-    <row r="46" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="W46" s="3" t="s">
         <v>26</v>
@@ -4828,7 +4900,7 @@
       <c r="DO46" s="2"/>
       <c r="DP46" s="2"/>
     </row>
-    <row r="47" spans="1:120" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>603</v>
       </c>
@@ -4850,7 +4922,7 @@
       <c r="DO47" s="2"/>
       <c r="DP47" s="2"/>
     </row>
-    <row r="48" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:120" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>18</v>
       </c>
@@ -4867,7 +4939,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="49" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>19</v>
       </c>
@@ -4884,7 +4956,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="50" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>604</v>
       </c>
@@ -4897,7 +4969,7 @@
       <c r="BO50" s="2"/>
       <c r="CH50" s="2"/>
     </row>
-    <row r="51" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>21</v>
       </c>
@@ -4910,7 +4982,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="52" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>22</v>
       </c>
@@ -4923,7 +4995,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="53" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>23</v>
       </c>
@@ -4937,7 +5009,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="54" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>722</v>
       </c>
@@ -4951,7 +5023,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="55" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>605</v>
       </c>
@@ -4965,7 +5037,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="56" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="W56" s="3" t="s">
         <v>732</v>
@@ -4977,7 +5049,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="57" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>606</v>
       </c>
@@ -4989,7 +5061,7 @@
       </c>
       <c r="CH57" s="2"/>
     </row>
-    <row r="58" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>607</v>
       </c>
@@ -5001,7 +5073,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="59" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>608</v>
       </c>
@@ -5010,7 +5082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>609</v>
       </c>
@@ -5021,7 +5093,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="61" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>610</v>
       </c>
@@ -5032,7 +5104,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="62" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="AT62" s="3" t="s">
         <v>660</v>
@@ -5041,7 +5113,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="63" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>611</v>
       </c>
@@ -5052,7 +5124,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="64" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>612</v>
       </c>
@@ -5063,7 +5135,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="65" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>20</v>
       </c>
@@ -5074,7 +5146,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="66" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>613</v>
       </c>
@@ -5083,7 +5155,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="67" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>614</v>
       </c>
@@ -5092,7 +5164,7 @@
       </c>
       <c r="CH67" s="2"/>
     </row>
-    <row r="68" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>615</v>
       </c>
@@ -5103,7 +5175,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="69" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>616</v>
       </c>
@@ -5114,7 +5186,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="70" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>617</v>
       </c>
@@ -5125,7 +5197,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="71" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>618</v>
       </c>
@@ -5134,7 +5206,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="72" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>723</v>
       </c>
@@ -5142,7 +5214,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="73" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>724</v>
       </c>
@@ -5150,13 +5222,13 @@
         <v>700</v>
       </c>
     </row>
-    <row r="74" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="CH74" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>619</v>
       </c>
@@ -5164,13 +5236,13 @@
         <v>701</v>
       </c>
     </row>
-    <row r="76" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>620</v>
       </c>
       <c r="CH76" s="2"/>
     </row>
-    <row r="77" spans="1:86" s="10" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>725</v>
       </c>
@@ -5178,7 +5250,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="78" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>621</v>
       </c>
@@ -5186,7 +5258,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="79" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>617</v>
       </c>
@@ -5194,7 +5266,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="80" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:86" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>726</v>
       </c>
@@ -5202,7 +5274,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="81" spans="1:86" s="10" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:86" s="10" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>622</v>
       </c>
@@ -5210,16 +5282,16 @@
         <v>705</v>
       </c>
     </row>
-    <row r="82" spans="1:86" s="10" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:86" s="10" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="CH82" s="3"/>
     </row>
-    <row r="83" spans="1:86" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:86" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="84" spans="1:86" ht="15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>29</v>
       </c>
@@ -5230,7 +5302,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="85" spans="1:86" ht="15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
         <v>382</v>
       </c>
@@ -5241,7 +5313,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="86" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>30</v>
       </c>
@@ -5252,7 +5324,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="87" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>383</v>
       </c>
@@ -5263,7 +5335,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="88" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>384</v>
       </c>
@@ -5274,7 +5346,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>385</v>
       </c>
@@ -5285,19 +5357,19 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>31</v>
       </c>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:86" ht="15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
       <c r="S91" s="3" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="92" spans="1:86" ht="15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>386</v>
       </c>
@@ -5305,7 +5377,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="93" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>387</v>
       </c>
@@ -5313,7 +5385,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="94" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>12</v>
       </c>
@@ -5321,7 +5393,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="95" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>388</v>
       </c>
@@ -5329,7 +5401,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="96" spans="1:86" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>389</v>
       </c>
@@ -5337,41 +5409,41 @@
         <v>39</v>
       </c>
     </row>
-    <row r="97" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="99" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:52" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:52" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:52" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="104" spans="1:52" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="105" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>45</v>
       </c>
@@ -5385,7 +5457,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="106" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
         <v>400</v>
       </c>
@@ -5399,7 +5471,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="107" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>46</v>
       </c>
@@ -5415,7 +5487,7 @@
       <c r="AY107" s="12"/>
       <c r="AZ107" s="12"/>
     </row>
-    <row r="108" spans="1:52" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>47</v>
       </c>
@@ -5431,7 +5503,7 @@
       <c r="AY108" s="12"/>
       <c r="AZ108" s="12"/>
     </row>
-    <row r="109" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>48</v>
       </c>
@@ -5443,7 +5515,7 @@
       </c>
       <c r="AX109" s="4"/>
     </row>
-    <row r="110" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>49</v>
       </c>
@@ -5455,13 +5527,13 @@
       </c>
       <c r="AX110" s="4"/>
     </row>
-    <row r="111" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="S111" s="3"/>
       <c r="AK111" s="3"/>
       <c r="AX111" s="3"/>
     </row>
-    <row r="112" spans="1:52" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>401</v>
       </c>
@@ -5473,7 +5545,7 @@
       </c>
       <c r="AX112" s="3"/>
     </row>
-    <row r="113" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>50</v>
       </c>
@@ -5485,7 +5557,7 @@
       </c>
       <c r="AX113" s="4"/>
     </row>
-    <row r="114" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>27</v>
       </c>
@@ -5497,7 +5569,7 @@
       </c>
       <c r="AX114" s="4"/>
     </row>
-    <row r="115" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>51</v>
       </c>
@@ -5509,7 +5581,7 @@
       </c>
       <c r="AX115" s="4"/>
     </row>
-    <row r="116" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
         <v>52</v>
       </c>
@@ -5517,41 +5589,41 @@
         <v>409</v>
       </c>
     </row>
-    <row r="117" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
     </row>
-    <row r="118" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="119" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="121" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="123" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:51" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:51" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="124" spans="1:51" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="125" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>65</v>
       </c>
@@ -5565,7 +5637,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="126" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
         <v>416</v>
       </c>
@@ -5579,7 +5651,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="127" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>417</v>
       </c>
@@ -5593,7 +5665,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="128" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>418</v>
       </c>
@@ -5607,7 +5679,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="129" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>419</v>
       </c>
@@ -5621,7 +5693,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="130" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>420</v>
       </c>
@@ -5635,7 +5707,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="131" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
         <v>421</v>
       </c>
@@ -5643,7 +5715,7 @@
       <c r="AJ131" s="3"/>
       <c r="AY131" s="3"/>
     </row>
-    <row r="132" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
       <c r="U132" s="3" t="s">
         <v>432</v>
@@ -5655,7 +5727,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="133" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>422</v>
       </c>
@@ -5669,7 +5741,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="134" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>423</v>
       </c>
@@ -5683,7 +5755,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="135" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>424</v>
       </c>
@@ -5697,7 +5769,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="136" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>425</v>
       </c>
@@ -5711,19 +5783,19 @@
         <v>456</v>
       </c>
     </row>
-    <row r="137" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>426</v>
       </c>
       <c r="AJ137" s="3"/>
     </row>
-    <row r="138" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A138" s="3"/>
       <c r="AJ138" s="3" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="139" spans="1:51" ht="15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>427</v>
       </c>
@@ -5731,7 +5803,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="140" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>428</v>
       </c>
@@ -5739,7 +5811,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="141" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>429</v>
       </c>
@@ -5747,7 +5819,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="142" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>430</v>
       </c>
@@ -5755,13 +5827,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="143" spans="1:51" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:51" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:51" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="144" spans="1:51" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="5" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="145" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>78</v>
       </c>
@@ -5775,1582 +5847,1623 @@
         <v>92</v>
       </c>
     </row>
-    <row r="146" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A146" s="14" t="s">
         <v>776</v>
       </c>
       <c r="R146" s="3" t="s">
-        <v>462</v>
+        <v>779</v>
       </c>
       <c r="AG146" s="3" t="s">
         <v>475</v>
       </c>
       <c r="AV146" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="147" spans="1:48" x14ac:dyDescent="0.2">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="147" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="R147" s="4" t="s">
-        <v>463</v>
-      </c>
+      <c r="R147" s="4"/>
       <c r="AG147" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="AV147" s="4" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="148" spans="1:48" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="R148" s="4" t="s">
-        <v>464</v>
+      <c r="R148" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="AG148" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AV148" s="4" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="149" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="AV148" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="149" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A149" s="4"/>
       <c r="R149" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="AG149" s="4" t="s">
         <v>87</v>
       </c>
       <c r="AV149" s="4" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="150" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="150" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
         <v>457</v>
       </c>
       <c r="R150" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="AG150" s="4" t="s">
         <v>88</v>
       </c>
       <c r="AV150" s="4" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="151" spans="1:48" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="151" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="R151" s="3"/>
+      <c r="R151" s="4" t="s">
+        <v>465</v>
+      </c>
       <c r="AG151" s="3"/>
-    </row>
-    <row r="152" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="AV151" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="152" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="R152" s="3" t="s">
-        <v>467</v>
+      <c r="R152" s="4" t="s">
+        <v>466</v>
       </c>
       <c r="AG152" s="3" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="153" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="AV152" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="153" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="R153" s="4" t="s">
-        <v>468</v>
-      </c>
+      <c r="R153" s="3"/>
       <c r="AG153" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="R154" s="4" t="s">
-        <v>469</v>
+      <c r="R154" s="3" t="s">
+        <v>467</v>
       </c>
       <c r="AG154" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="155" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A155" s="3"/>
       <c r="R155" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AG155" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="156" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
         <v>460</v>
       </c>
       <c r="R156" s="4" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="157" spans="1:48" x14ac:dyDescent="0.2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="157" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="R157" s="3"/>
-    </row>
-    <row r="158" spans="1:48" ht="15" x14ac:dyDescent="0.2">
+      <c r="R157" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="158" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="R158" s="3" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="159" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="R158" s="4" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="159" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="R159" s="4" t="s">
+      <c r="R159" s="3"/>
+    </row>
+    <row r="160" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="R160" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="161" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R161" s="4" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="160" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="R160" s="4" t="s">
+    <row r="162" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="R162" s="4" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="161" spans="1:45" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="R161" s="4" t="s">
+    <row r="163" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="Q163" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="R163" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="162" spans="1:45" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="5" t="s">
+    <row r="165" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="R165" s="3" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="166" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="S166" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="167" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="S167" s="2" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="169" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="R169" s="3" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="170" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="S170" s="2" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="171" spans="1:45" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="172" spans="1:45" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="5" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="163" spans="1:45" ht="15" x14ac:dyDescent="0.2">
-      <c r="A163" s="1" t="s">
+    <row r="173" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="S163" s="1" t="s">
+      <c r="S173" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AF163" s="1" t="s">
+      <c r="AF173" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AS163" s="1" t="s">
+      <c r="AS173" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="164" spans="1:45" ht="15" x14ac:dyDescent="0.2">
-      <c r="A164" s="3" t="s">
+    <row r="174" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A174" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="S164" s="3" t="s">
+      <c r="S174" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="AF164" s="3" t="s">
+      <c r="AF174" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="AS164" s="3" t="s">
+      <c r="AS174" s="3" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="165" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A165" s="4" t="s">
+    <row r="175" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="S165" s="4" t="s">
+      <c r="S175" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="AF165" s="4" t="s">
+      <c r="AF175" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="AS165" s="4" t="s">
+      <c r="AS175" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="166" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A166" s="4" t="s">
+    <row r="176" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="S166" s="4" t="s">
+      <c r="S176" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AF166" s="4" t="s">
+      <c r="AF176" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="AS166" s="4" t="s">
+      <c r="AS176" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="167" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A167" s="4" t="s">
+    <row r="177" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="S167" s="3"/>
-      <c r="AF167" s="3"/>
-      <c r="AS167" s="4" t="s">
+      <c r="S177" s="3"/>
+      <c r="AF177" s="3"/>
+      <c r="AS177" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="168" spans="1:45" ht="15" x14ac:dyDescent="0.2">
-      <c r="A168" s="3"/>
-      <c r="S168" s="3" t="s">
+    <row r="178" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A178" s="3"/>
+      <c r="S178" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="AF168" s="3" t="s">
+      <c r="AF178" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="AS168" s="3"/>
-    </row>
-    <row r="169" spans="1:45" ht="15" x14ac:dyDescent="0.2">
-      <c r="A169" s="3" t="s">
+      <c r="AS178" s="3"/>
+    </row>
+    <row r="179" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A179" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="S169" s="4" t="s">
+      <c r="S179" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="AF169" s="4" t="s">
+      <c r="AF179" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="AS169" s="3" t="s">
+      <c r="AS179" s="3" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="170" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A170" s="4" t="s">
+    <row r="180" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="S170" s="4" t="s">
+      <c r="S180" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="AF170" s="4" t="s">
+      <c r="AF180" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="AS170" s="4" t="s">
+      <c r="AS180" s="4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="171" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A171" s="4" t="s">
+    <row r="181" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AF171" s="4" t="s">
+      <c r="AF181" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="AS171" s="4" t="s">
+      <c r="AS181" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="172" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A172" s="3"/>
-      <c r="AF172" s="3"/>
-    </row>
-    <row r="173" spans="1:45" ht="15" x14ac:dyDescent="0.2">
-      <c r="A173" s="3" t="s">
+    <row r="182" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A182" s="3"/>
+      <c r="AF182" s="3"/>
+    </row>
+    <row r="183" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="AF173" s="3" t="s">
+      <c r="AF183" s="3" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="174" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A174" s="4" t="s">
+    <row r="184" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AF174" s="4" t="s">
+      <c r="AF184" s="4" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="175" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A175" s="4" t="s">
+    <row r="185" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="AF175" s="4" t="s">
+      <c r="AF185" s="4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="176" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="A176" s="4" t="s">
+    <row r="186" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="177" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A177" s="4" t="s">
+    <row r="187" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="178" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A178" s="3"/>
-    </row>
-    <row r="179" spans="1:33" ht="15" x14ac:dyDescent="0.2">
-      <c r="A179" s="3" t="s">
+    <row r="188" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A188" s="3"/>
+    </row>
+    <row r="189" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="180" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A180" s="4" t="s">
+    <row r="190" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="181" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A181" s="4" t="s">
+    <row r="191" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="182" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A182" s="4" t="s">
+    <row r="192" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="183" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A183" s="4" t="s">
+    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="185" spans="1:33" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="5" t="s">
+    <row r="194" spans="1:33" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="195" spans="1:33" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="5" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="186" spans="1:33" ht="15" x14ac:dyDescent="0.2">
-      <c r="A186" s="1" t="s">
+    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="R186" s="1" t="s">
+      <c r="R196" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="AG186" s="1" t="s">
+      <c r="AG196" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="187" spans="1:33" ht="15" x14ac:dyDescent="0.2">
-      <c r="A187" s="3" t="s">
+    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="R187" s="3" t="s">
+      <c r="R197" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="AG187" s="3" t="s">
+      <c r="AG197" s="3" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="188" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A188" s="4" t="s">
+    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="R188" s="4" t="s">
+      <c r="R198" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="AG188" s="4" t="s">
+      <c r="AG198" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="189" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A189" s="4" t="s">
+    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="R189" s="4" t="s">
+      <c r="R199" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="AG189" s="4" t="s">
+      <c r="AG199" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="190" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A190" s="4" t="s">
+    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="R190" s="4" t="s">
+      <c r="R200" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AG190" s="4" t="s">
+      <c r="AG200" s="4" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="191" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A191" s="3"/>
-      <c r="R191" s="3"/>
-      <c r="AG191" s="3"/>
-    </row>
-    <row r="192" spans="1:33" ht="15" x14ac:dyDescent="0.2">
-      <c r="A192" s="3" t="s">
+    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A201" s="3"/>
+      <c r="R201" s="3"/>
+      <c r="AG201" s="3"/>
+    </row>
+    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="R192" s="3" t="s">
+      <c r="R202" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="AG192" s="3" t="s">
+      <c r="AG202" s="3" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="193" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A193" s="4" t="s">
+    <row r="203" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="R193" s="4" t="s">
+      <c r="R203" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="AG193" s="4" t="s">
+      <c r="AG203" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="194" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A194" s="4" t="s">
+    <row r="204" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="R194" s="4" t="s">
+      <c r="R204" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AG194" s="4" t="s">
+      <c r="AG204" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="195" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A195" s="4" t="s">
+    <row r="205" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="R195" s="4" t="s">
+      <c r="R205" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="AG195" s="4" t="s">
+      <c r="AG205" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="196" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A196" s="3"/>
-      <c r="R196" s="3"/>
-      <c r="AG196" s="3"/>
-    </row>
-    <row r="197" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A197" s="3" t="s">
+    <row r="206" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A206" s="3"/>
+      <c r="R206" s="3"/>
+      <c r="AG206" s="3"/>
+    </row>
+    <row r="207" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="R197" s="3" t="s">
+      <c r="R207" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="AG197" s="3" t="s">
+      <c r="AG207" s="3" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="198" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A198" s="4" t="s">
+    <row r="208" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="R198" s="4" t="s">
+      <c r="R208" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="AG198" s="4" t="s">
+      <c r="AG208" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="199" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A199" s="4" t="s">
+    <row r="209" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="R199" s="4" t="s">
+      <c r="R209" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="AG199" s="4" t="s">
+      <c r="AG209" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="200" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A200" s="4" t="s">
+    <row r="210" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="R200" s="4" t="s">
+      <c r="R210" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="AG200" s="4" t="s">
+      <c r="AG210" s="4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="201" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="202" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="5" t="s">
+    <row r="211" spans="1:48" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="212" spans="1:48" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="5" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="203" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A203" s="1" t="s">
+    <row r="213" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A213" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="R203" s="1" t="s">
+      <c r="R213" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="AG203" s="1" t="s">
+      <c r="AG213" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AV203" s="1" t="s">
+      <c r="AV213" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="204" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A204" s="3" t="s">
+    <row r="214" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="R204" s="3" t="s">
+      <c r="R214" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="AG204" s="3" t="s">
+      <c r="AG214" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="AV204" s="3" t="s">
+      <c r="AV214" s="3" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="205" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A205" s="4" t="s">
+    <row r="215" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="R205" s="4" t="s">
+      <c r="R215" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="AG205" s="4" t="s">
+      <c r="AG215" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="AV205" s="4" t="s">
+      <c r="AV215" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="206" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A206" s="4" t="s">
+    <row r="216" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="R206" s="4" t="s">
+      <c r="R216" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="AG206" s="4" t="s">
+      <c r="AG216" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="AV206" s="4" t="s">
+      <c r="AV216" s="4" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="207" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A207" s="4" t="s">
+    <row r="217" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="R207" s="4" t="s">
+      <c r="R217" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="AG207" s="4" t="s">
+      <c r="AG217" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="AV207" s="4" t="s">
+      <c r="AV217" s="4" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="208" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A208" s="4" t="s">
+    <row r="218" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="R208" s="4" t="s">
+      <c r="R218" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="AG208" s="4" t="s">
+      <c r="AG218" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="AV208" s="4" t="s">
+      <c r="AV218" s="4" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="209" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A209" s="3"/>
-      <c r="R209" s="3"/>
-      <c r="AG209" s="3"/>
-      <c r="AV209" s="3"/>
-    </row>
-    <row r="210" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A210" s="3" t="s">
+    <row r="219" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A219" s="3"/>
+      <c r="R219" s="3"/>
+      <c r="AG219" s="3"/>
+      <c r="AV219" s="3"/>
+    </row>
+    <row r="220" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A220" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="R210" s="3" t="s">
+      <c r="R220" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="AG210" s="3" t="s">
+      <c r="AG220" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="AV210" s="3" t="s">
+      <c r="AV220" s="3" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="211" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A211" s="4" t="s">
+    <row r="221" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="R211" s="4" t="s">
+      <c r="R221" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="AG211" s="4" t="s">
+      <c r="AG221" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="AV211" s="4" t="s">
+      <c r="AV221" s="4" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="212" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A212" s="4" t="s">
+    <row r="222" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="R212" s="4" t="s">
+      <c r="R222" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AG212" s="4" t="s">
+      <c r="AG222" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="AV212" s="4" t="s">
+      <c r="AV222" s="4" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="213" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A213" s="4" t="s">
+    <row r="223" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="R213" s="4" t="s">
+      <c r="R223" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AG213" s="4" t="s">
+      <c r="AG223" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="AV213" s="4" t="s">
+      <c r="AV223" s="4" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="214" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A214" s="4" t="s">
+    <row r="224" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="R214" s="4" t="s">
+      <c r="R224" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="AG214" s="4" t="s">
+      <c r="AG224" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="AV214" s="4" t="s">
+      <c r="AV224" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="215" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="R215" s="3"/>
-    </row>
-    <row r="216" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="R216" s="3" t="s">
+    <row r="225" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="R225" s="3"/>
+    </row>
+    <row r="226" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="R226" s="3" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="217" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="R217" s="4" t="s">
+    <row r="227" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="R227" s="4" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="218" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="R218" s="4" t="s">
+    <row r="228" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="R228" s="4" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="219" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="R219" s="4" t="s">
+    <row r="229" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="R229" s="4" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="220" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="R220" s="4" t="s">
+    <row r="230" spans="1:48" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R230" s="4" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="221" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="5" t="s">
+    <row r="231" spans="1:48" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="5" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="222" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A222" s="1" t="s">
+    <row r="232" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A232" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="R222" s="1" t="s">
+      <c r="R232" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="AE222" s="1" t="s">
+      <c r="AE232" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="AV222" s="1" t="s">
+      <c r="AV232" s="1" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="223" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A223" s="3" t="s">
+    <row r="233" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A233" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="R223" s="3" t="s">
+      <c r="R233" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="AE223" s="3" t="s">
+      <c r="AE233" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="AV223" s="3" t="s">
+      <c r="AV233" s="3" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="224" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A224" s="4" t="s">
+    <row r="234" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="R224" s="4" t="s">
+      <c r="R234" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="AE224" s="4" t="s">
+      <c r="AE234" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="AV224" s="4" t="s">
+      <c r="AV234" s="4" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="225" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A225" s="4" t="s">
+    <row r="235" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="R225" s="4" t="s">
+      <c r="R235" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="AE225" s="4" t="s">
+      <c r="AE235" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="AV225" s="4" t="s">
+      <c r="AV235" s="4" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="226" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A226" s="4" t="s">
+    <row r="236" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="R226" s="4" t="s">
+      <c r="R236" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="AE226" s="4" t="s">
+      <c r="AE236" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="AV226" s="4" t="s">
+      <c r="AV236" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="227" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A227" s="4" t="s">
+    <row r="237" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="R227" s="4" t="s">
+      <c r="R237" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="AE227" s="4" t="s">
+      <c r="AE237" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="AV227" s="4" t="s">
+      <c r="AV237" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="228" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A228" s="3"/>
-      <c r="R228" s="3"/>
-      <c r="AE228" s="3"/>
-      <c r="AV228" s="3"/>
-    </row>
-    <row r="229" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A229" s="3" t="s">
+    <row r="238" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A238" s="3"/>
+      <c r="R238" s="3"/>
+      <c r="AE238" s="3"/>
+      <c r="AV238" s="3"/>
+    </row>
+    <row r="239" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A239" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="R229" s="3" t="s">
+      <c r="R239" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="AE229" s="3" t="s">
+      <c r="AE239" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="AV229" s="3" t="s">
+      <c r="AV239" s="3" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="230" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A230" s="4" t="s">
+    <row r="240" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="R230" s="4" t="s">
+      <c r="R240" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="AE230" s="4" t="s">
+      <c r="AE240" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="AV230" s="4" t="s">
+      <c r="AV240" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="231" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A231" s="4" t="s">
+    <row r="241" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="R231" s="4" t="s">
+      <c r="R241" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="AE231" s="4" t="s">
+      <c r="AE241" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="AV231" s="4" t="s">
+      <c r="AV241" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="232" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A232" s="4" t="s">
+    <row r="242" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="R232" s="4" t="s">
+      <c r="R242" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="AE232" s="4" t="s">
+      <c r="AE242" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="AV232" s="4" t="s">
+      <c r="AV242" s="4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="233" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A233" s="4" t="s">
+    <row r="243" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="R233" s="4" t="s">
+      <c r="R243" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="AE233" s="4" t="s">
+      <c r="AE243" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="AV233" s="4" t="s">
+      <c r="AV243" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="234" spans="1:48" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="R234" s="4" t="s">
+    <row r="244" spans="1:48" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R244" s="4" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="235" spans="1:48" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="236" spans="1:48" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="5" t="s">
+    <row r="245" spans="1:48" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="246" spans="1:48" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="5" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="237" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A237" s="1" t="s">
+    <row r="247" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A247" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="R237" s="1" t="s">
+      <c r="R247" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="AG237" s="1" t="s">
+      <c r="AG247" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="238" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A238" s="3" t="s">
+    <row r="248" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A248" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="R238" s="3" t="s">
+      <c r="R248" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="AG238" s="3" t="s">
+      <c r="AG248" s="3" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="239" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A239" s="4" t="s">
+    <row r="249" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="R239" s="4" t="s">
+      <c r="R249" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="AG239" s="4" t="s">
+      <c r="AG249" s="4" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="240" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A240" s="4" t="s">
+    <row r="250" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="R240" s="4" t="s">
+      <c r="R250" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="AG240" s="4" t="s">
+      <c r="AG250" s="4" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="241" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A241" s="4" t="s">
+    <row r="251" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="R241" s="4" t="s">
+      <c r="R251" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="AG241" s="4" t="s">
+      <c r="AG251" s="4" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="242" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A242" s="3"/>
-      <c r="R242" s="3"/>
-      <c r="AG242" s="3"/>
-    </row>
-    <row r="243" spans="1:33" ht="15" x14ac:dyDescent="0.2">
-      <c r="A243" s="3" t="s">
+    <row r="252" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A252" s="3"/>
+      <c r="R252" s="3"/>
+      <c r="AG252" s="3"/>
+    </row>
+    <row r="253" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A253" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="R243" s="3" t="s">
+      <c r="R253" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="AG243" s="3" t="s">
+      <c r="AG253" s="3" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="244" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A244" s="4" t="s">
+    <row r="254" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="R244" s="4" t="s">
+      <c r="R254" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="AG244" s="4" t="s">
+      <c r="AG254" s="4" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="245" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A245" s="4" t="s">
+    <row r="255" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="R245" s="4" t="s">
+      <c r="R255" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="AG245" s="4" t="s">
+      <c r="AG255" s="4" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="246" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A246" s="4" t="s">
+    <row r="256" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="R246" s="4" t="s">
+      <c r="R256" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="AG246" s="4" t="s">
+      <c r="AG256" s="4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A247" s="3"/>
-      <c r="R247" s="3"/>
-      <c r="AG247" s="4" t="s">
+    <row r="257" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A257" s="3"/>
+      <c r="R257" s="3"/>
+      <c r="AG257" s="4" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="248" spans="1:33" ht="15" x14ac:dyDescent="0.2">
-      <c r="A248" s="3" t="s">
+    <row r="258" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A258" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="R248" s="3" t="s">
+      <c r="R258" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="AG248" s="3"/>
-    </row>
-    <row r="249" spans="1:33" ht="15" x14ac:dyDescent="0.2">
-      <c r="A249" s="4" t="s">
+      <c r="AG258" s="3"/>
+    </row>
+    <row r="259" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="R249" s="4" t="s">
+      <c r="R259" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="AG249" s="3" t="s">
+      <c r="AG259" s="3" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A250" s="4" t="s">
+    <row r="260" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="R250" s="4" t="s">
+      <c r="R260" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="AG250" s="4" t="s">
+      <c r="AG260" s="4" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A251" s="4" t="s">
+    <row r="261" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="R251" s="4" t="s">
+      <c r="R261" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="AG251" s="4" t="s">
+      <c r="AG261" s="4" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="252" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A252" s="3"/>
-      <c r="AG252" s="4" t="s">
+    <row r="262" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A262" s="3"/>
+      <c r="AG262" s="4" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="253" spans="1:33" ht="15" x14ac:dyDescent="0.2">
-      <c r="A253" s="3" t="s">
+    <row r="263" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A263" s="3" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="254" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A254" s="4" t="s">
+    <row r="264" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="255" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A255" s="4" t="s">
+    <row r="265" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="256" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A256" s="4" t="s">
+    <row r="266" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="257" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A257" s="3"/>
-    </row>
-    <row r="258" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="A258" s="3" t="s">
+    <row r="267" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A267" s="3"/>
+    </row>
+    <row r="268" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A268" s="3" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="259" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A259" s="4" t="s">
+    <row r="269" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="260" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A260" s="4" t="s">
+    <row r="270" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="261" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A261" s="4" t="s">
+    <row r="271" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="262" spans="1:49" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="263" spans="1:49" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="5" t="s">
+    <row r="272" spans="1:33" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="273" spans="1:49" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="5" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="264" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="A264" s="1" t="s">
+    <row r="274" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A274" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="R264" s="1" t="s">
+      <c r="R274" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AF264" s="1" t="s">
+      <c r="AF274" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="AW264" s="1" t="s">
+      <c r="AW274" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="265" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="A265" s="3" t="s">
+    <row r="275" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A275" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="R265" s="3" t="s">
+      <c r="R275" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="AF265" s="3" t="s">
+      <c r="AF275" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="AW265" s="3" t="s">
+      <c r="AW275" s="3" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="266" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A266" s="4" t="s">
+    <row r="276" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="R266" s="4" t="s">
+      <c r="R276" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="AF266" s="4" t="s">
+      <c r="AF276" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="AW266" s="4" t="s">
+      <c r="AW276" s="4" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="267" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A267" s="4" t="s">
+    <row r="277" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="R267" s="4" t="s">
+      <c r="R277" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="AF267" s="4" t="s">
+      <c r="AF277" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="AW267" s="4" t="s">
+      <c r="AW277" s="4" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="268" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A268" s="4" t="s">
+    <row r="278" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="R268" s="4" t="s">
+      <c r="R278" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="AF268" s="4" t="s">
+      <c r="AF278" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="AW268" s="4" t="s">
+      <c r="AW278" s="4" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="269" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A269" s="4" t="s">
+    <row r="279" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="R269" s="4" t="s">
+      <c r="R279" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="AF269" s="3"/>
-      <c r="AW269" s="4" t="s">
+      <c r="AF279" s="3"/>
+      <c r="AW279" s="4" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="270" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="A270" s="3"/>
-      <c r="R270" s="3"/>
-      <c r="AF270" s="3" t="s">
+    <row r="280" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A280" s="3"/>
+      <c r="R280" s="3"/>
+      <c r="AF280" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="AW270" s="3"/>
-    </row>
-    <row r="271" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="A271" s="3" t="s">
+      <c r="AW280" s="3"/>
+    </row>
+    <row r="281" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A281" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="R271" s="3" t="s">
+      <c r="R281" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="AF271" s="4" t="s">
+      <c r="AF281" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="AW271" s="3" t="s">
+      <c r="AW281" s="3" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="272" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A272" s="4" t="s">
+    <row r="282" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="R272" s="4" t="s">
+      <c r="R282" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="AF272" s="4" t="s">
+      <c r="AF282" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="AW272" s="4" t="s">
+      <c r="AW282" s="4" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="273" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A273" s="4" t="s">
+    <row r="283" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="R273" s="4" t="s">
+      <c r="R283" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="AF273" s="4" t="s">
+      <c r="AF283" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="AW273" s="4" t="s">
+      <c r="AW283" s="4" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="274" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A274" s="4" t="s">
+    <row r="284" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="R274" s="4" t="s">
+      <c r="R284" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="AW274" s="4" t="s">
+      <c r="AW284" s="4" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="275" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="A275" s="4" t="s">
+    <row r="285" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A285" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="R275" s="4" t="s">
+      <c r="R285" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="AW275" s="4" t="s">
+      <c r="AW285" s="4" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="276" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW276" s="4" t="s">
+    <row r="286" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW286" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="277" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW277" s="3"/>
-    </row>
-    <row r="278" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="AW278" s="3" t="s">
+    <row r="287" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW287" s="3"/>
+    </row>
+    <row r="288" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW288" s="3" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="279" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW279" s="4" t="s">
+    <row r="289" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW289" s="4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="280" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW280" s="4" t="s">
+    <row r="290" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW290" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="281" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW281" s="4" t="s">
+    <row r="291" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW291" s="4" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="282" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW282" s="4" t="s">
+    <row r="292" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW292" s="4" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="283" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW283" s="3"/>
-    </row>
-    <row r="284" spans="1:49" ht="15" x14ac:dyDescent="0.2">
-      <c r="AW284" s="3" t="s">
+    <row r="293" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW293" s="3"/>
+    </row>
+    <row r="294" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW294" s="3" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="285" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW285" s="4" t="s">
+    <row r="295" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW295" s="4" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="286" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW286" s="4" t="s">
+    <row r="296" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW296" s="4" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="287" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW287" s="4" t="s">
+    <row r="297" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW297" s="4" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="288" spans="1:49" x14ac:dyDescent="0.2">
-      <c r="AW288" s="4" t="s">
+    <row r="298" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AW298" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="289" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="290" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="5" t="s">
+    <row r="299" spans="1:49" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="300" spans="1:49" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="5" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="291" spans="1:31" ht="15" x14ac:dyDescent="0.2">
-      <c r="A291" s="1" t="s">
+    <row r="301" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A301" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="Q291" s="1" t="s">
+      <c r="Q301" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="AE291" s="1" t="s">
+      <c r="AE301" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="292" spans="1:31" ht="15" x14ac:dyDescent="0.2">
-      <c r="A292" s="3" t="s">
+    <row r="302" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A302" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="Q292" s="3" t="s">
+      <c r="Q302" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="AE292" s="3" t="s">
+      <c r="AE302" s="3" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="293" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A293" s="4" t="s">
+    <row r="303" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="Q293" s="4" t="s">
+      <c r="Q303" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="AE293" s="4" t="s">
+      <c r="AE303" s="4" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="294" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A294" s="4" t="s">
+    <row r="304" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="Q294" s="4" t="s">
+      <c r="Q304" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="AE294" s="4" t="s">
+      <c r="AE304" s="4" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="295" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A295" s="4" t="s">
+    <row r="305" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="Q295" s="4" t="s">
+      <c r="Q305" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="AE295" s="4" t="s">
+      <c r="AE305" s="4" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="296" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A296" s="4" t="s">
+    <row r="306" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="Q296" s="4" t="s">
+      <c r="Q306" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="AE296" s="4" t="s">
+      <c r="AE306" s="4" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="297" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A297" s="3"/>
-      <c r="Q297" s="3"/>
-      <c r="AE297" s="3"/>
-    </row>
-    <row r="298" spans="1:31" ht="15" x14ac:dyDescent="0.2">
-      <c r="A298" s="3" t="s">
+    <row r="307" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A307" s="3"/>
+      <c r="Q307" s="3"/>
+      <c r="AE307" s="3"/>
+    </row>
+    <row r="308" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="Q298" s="3" t="s">
+      <c r="Q308" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="AE298" s="3" t="s">
+      <c r="AE308" s="3" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="299" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A299" s="4" t="s">
+    <row r="309" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="Q299" s="4" t="s">
+      <c r="Q309" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AE299" s="4" t="s">
+      <c r="AE309" s="4" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="300" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A300" s="4" t="s">
+    <row r="310" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="Q300" s="4" t="s">
+      <c r="Q310" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="AE300" s="4" t="s">
+      <c r="AE310" s="4" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="301" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A301" s="4" t="s">
+    <row r="311" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="Q301" s="4" t="s">
+      <c r="Q311" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="AE301" s="4" t="s">
+      <c r="AE311" s="4" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="302" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A302" s="4" t="s">
+    <row r="312" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="Q302" s="4" t="s">
+      <c r="Q312" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="AE302" s="4" t="s">
+      <c r="AE312" s="4" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="303" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="304" spans="1:31" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="5" t="s">
+    <row r="313" spans="1:48" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="314" spans="1:48" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A314" s="5" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="305" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A305" s="1" t="s">
+    <row r="315" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A315" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="P305" s="1" t="s">
+      <c r="P315" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AE305" s="1" t="s">
+      <c r="AE315" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="AV305" s="1" t="s">
+      <c r="AV315" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="306" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A306" s="3" t="s">
+    <row r="316" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A316" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="P306" s="3" t="s">
+      <c r="P316" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="AE306" s="3" t="s">
+      <c r="AE316" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="AV306" s="3" t="s">
+      <c r="AV316" s="3" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="307" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A307" s="4" t="s">
+    <row r="317" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A317" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="P307" s="4" t="s">
+      <c r="P317" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="AE307" s="4" t="s">
+      <c r="AE317" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="AV307" s="4" t="s">
+      <c r="AV317" s="4" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="308" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A308" s="4" t="s">
+    <row r="318" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="P308" s="4" t="s">
+      <c r="P318" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="AE308" s="4" t="s">
+      <c r="AE318" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="AV308" s="4" t="s">
+      <c r="AV318" s="4" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="309" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A309" s="4" t="s">
+    <row r="319" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="P309" s="4" t="s">
+      <c r="P319" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="AE309" s="4" t="s">
+      <c r="AE319" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="AV309" s="4" t="s">
+      <c r="AV319" s="4" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="310" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A310" s="4" t="s">
+    <row r="320" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="P310" s="4" t="s">
+      <c r="P320" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="AE310" s="4" t="s">
+      <c r="AE320" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="AV310" s="4" t="s">
+      <c r="AV320" s="4" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="311" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A311" s="3"/>
-      <c r="P311" s="3"/>
-      <c r="AE311" s="3"/>
-      <c r="AV311" s="4" t="s">
+    <row r="321" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A321" s="3"/>
+      <c r="P321" s="3"/>
+      <c r="AE321" s="3"/>
+      <c r="AV321" s="4" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="312" spans="1:48" ht="15" x14ac:dyDescent="0.2">
-      <c r="A312" s="3" t="s">
+    <row r="322" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="P312" s="3" t="s">
+      <c r="P322" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="AE312" s="3" t="s">
+      <c r="AE322" s="3" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="313" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A313" s="4" t="s">
+    <row r="323" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A323" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="P313" s="4" t="s">
+      <c r="P323" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="AE313" s="4" t="s">
+      <c r="AE323" s="4" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="314" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A314" s="4" t="s">
+    <row r="324" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="P314" s="4" t="s">
+      <c r="P324" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="AE314" s="4" t="s">
+      <c r="AE324" s="4" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="315" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A315" s="4" t="s">
+    <row r="325" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A325" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="P315" s="4" t="s">
+      <c r="P325" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AE315" s="4" t="s">
+      <c r="AE325" s="4" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="316" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A316" s="4" t="s">
+    <row r="326" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="P316" s="4" t="s">
+      <c r="P326" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="AE316" s="4" t="s">
+      <c r="AE326" s="4" t="s">
         <v>338</v>
       </c>
     </row>
